--- a/sheets/S08A22P220.xlsx
+++ b/sheets/S08A22P220.xlsx
@@ -20194,7 +20194,7 @@
         <v>13</v>
       </c>
       <c r="G595" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H595" t="s">
         <v>15</v>
@@ -20220,7 +20220,7 @@
         <v>13</v>
       </c>
       <c r="G596" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H596" t="s">
         <v>15</v>
@@ -20246,7 +20246,7 @@
         <v>13</v>
       </c>
       <c r="G597" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H597" t="s">
         <v>15</v>
@@ -20272,7 +20272,7 @@
         <v>13</v>
       </c>
       <c r="G598" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H598" t="s">
         <v>15</v>
@@ -20298,7 +20298,7 @@
         <v>13</v>
       </c>
       <c r="G599" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H599" t="s">
         <v>15</v>
@@ -20324,7 +20324,7 @@
         <v>13</v>
       </c>
       <c r="G600" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H600" t="s">
         <v>15</v>
@@ -20350,7 +20350,7 @@
         <v>13</v>
       </c>
       <c r="G601" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H601" t="s">
         <v>15</v>
@@ -20376,7 +20376,7 @@
         <v>13</v>
       </c>
       <c r="G602" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H602" t="s">
         <v>15</v>
